--- a/artfynd/A 50161-2021 artfynd.xlsx
+++ b/artfynd/A 50161-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66354977</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75772849</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66354958</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1147,8 +1167,19 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85201252</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 50161-2021 artfynd.xlsx
+++ b/artfynd/A 50161-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1170,6 +1170,366 @@
       <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/85201252</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136439742</v>
+      </c>
+      <c r="B6" t="n">
+        <v>110045</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sydväst om Sibbarp, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>428670</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6427862</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Främst i innerslänt men även i dikesbotten. Spritt längs en sträcka av ca 3 meter längs väg, ca 1,5 m på var sida av denna punkt</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg, Jennifer Gao</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136439742</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136439743</v>
+      </c>
+      <c r="B7" t="n">
+        <v>110308</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sydväst om Sibbarp, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>428664</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6427865</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Samlat bestånd, på södra sidan av vägen. I innerslänt, nära stödremsan</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg, Jennifer Gao</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136439743</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136439734</v>
+      </c>
+      <c r="B8" t="n">
+        <v>102776</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Öster om Sandhem, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>428697</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6427865</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sandhem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Främst i ytterslänt på norra sidan om vägen. Längs ca åtta meter.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg, Jennifer Gao</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136439734</t>
         </is>
       </c>
     </row>
@@ -1179,6 +1539,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50161-2021 artfynd.xlsx
+++ b/artfynd/A 50161-2021 artfynd.xlsx
@@ -1178,7 +1178,7 @@
         <v>136439742</v>
       </c>
       <c r="B6" t="n">
-        <v>110045</v>
+        <v>110058</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>136439743</v>
       </c>
       <c r="B7" t="n">
-        <v>110308</v>
+        <v>110321</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>136439734</v>
       </c>
       <c r="B8" t="n">
-        <v>102776</v>
+        <v>102789</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 50161-2021 artfynd.xlsx
+++ b/artfynd/A 50161-2021 artfynd.xlsx
@@ -1178,7 +1178,7 @@
         <v>136439742</v>
       </c>
       <c r="B6" t="n">
-        <v>110058</v>
+        <v>110059</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>136439743</v>
       </c>
       <c r="B7" t="n">
-        <v>110321</v>
+        <v>110322</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>136439734</v>
       </c>
       <c r="B8" t="n">
-        <v>102789</v>
+        <v>102790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
